--- a/bot_invoice/samples/EK-2029_qr_import.xlsx
+++ b/bot_invoice/samples/EK-2029_qr_import.xlsx
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2392.75</v>
+        <v>2177.4</v>
       </c>
       <c r="H5" t="n">
         <v>989.73</v>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>151.32</v>
+        <v>139.21</v>
       </c>
       <c r="H12" t="n">
         <v>1898.32</v>

--- a/bot_invoice/samples/EK-2029_qr_import.xlsx
+++ b/bot_invoice/samples/EK-2029_qr_import.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EK-2029 import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="import" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/bot_invoice/samples/EK-2029_qr_import.xlsx
+++ b/bot_invoice/samples/EK-2029_qr_import.xlsx
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>556.4299999999999</v>
+        <v>865.5599999999999</v>
       </c>
       <c r="H7" t="n">
         <v>319.26</v>
